--- a/Alumnos_exportados.xlsx
+++ b/Alumnos_exportados.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>GABRIEL</t>
+          <t>GABRIEL ARMANDO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -522,7 +522,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KEVIN</t>
+          <t>KEVIN ANDRES (Atencion)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AXEL</t>
+          <t>AXEL ARMANDO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>IRVING</t>
+          <t>IRVING DANIEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SAHILY</t>
+          <t>SAHILY MICHELLE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>CARLOS IVAN</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>RUBI</t>
+          <t>RUBI ESMERALDA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CLAUDIA</t>
+          <t>CLAUDIA ELIZABETH</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BRISA</t>
+          <t>BRISA SUGEY</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>JUAN</t>
+          <t>JUAN AARON (Atencion)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DULCE</t>
+          <t>DULCE AURORA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EVELYN</t>
+          <t>EVELYN BRICEIDA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>IAN</t>
+          <t>IAN GAEL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ENRIQUE</t>
+          <t>ENRIQUE (Atencion)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ANNIE</t>
+          <t>ANNIE CAMILA (Discap)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>HILARY</t>
+          <t>HILARY JUANITA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ABRIL</t>
+          <t>ABRIL DANIELA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>MARIO</t>
+          <t>MARIO AARON</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>OLLAN</t>
+          <t>OLLAN ROBERTO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FERNANDA</t>
+          <t>FERNANDA VALENTINA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>JOSHUA</t>
+          <t>JOSHUA EDUARDO</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PABLO</t>
+          <t>PABLO GIOVANNY</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>ANGEL RAFAEL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KENNY</t>
+          <t>KENNY DANIEL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ROSA</t>
+          <t>ROSA ESPERANZA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>XARENI</t>
+          <t>XARENI AURORA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>JAQUELIN</t>
+          <t>JAQUELIN ALEXANDRA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1984,7 +1984,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>KAMIL</t>
+          <t>KAMIL ALEJANDRO</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>AARON</t>
+          <t>AARON GAEL JG</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>RAPHAEL</t>
+          <t>RAPHAEL ALEXANDER</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>JOSE FRANCISCO</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DYLAN</t>
+          <t>DYLAN ISAAC</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ALAN</t>
+          <t>ALAN AARON</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ESTELA</t>
+          <t>ESTELA BRISEL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CARLOS</t>
+          <t>CARLOS FARITH</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FABIOLA</t>
+          <t>FABIOLA ELENA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>MARIA</t>
+          <t>MARIA XIMENA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>YARETZI</t>
+          <t>YARETZI ESMERALDA SEC</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SERGIO</t>
+          <t>SERGIO IVAN</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ANGEL</t>
+          <t>ANGEL YAIR</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>JOSE GUILLERMO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>JOSE</t>
+          <t>JOSE HAZAEL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>URIEL</t>
+          <t>URIEL IÑAKI</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>del</t>
+          <t>del Carmen</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
